--- a/sites_updated.xlsx
+++ b/sites_updated.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1113" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1205" uniqueCount="267">
   <si>
     <t>site_name</t>
   </si>
@@ -58,6 +58,9 @@
     <t>track</t>
   </si>
   <si>
+    <t>owner_step</t>
+  </si>
+  <si>
     <t>official_flag</t>
   </si>
   <si>
@@ -76,15 +79,15 @@
     <t>crawl_scope</t>
   </si>
   <si>
-    <t>owner_step</t>
-  </si>
-  <si>
     <t>memo</t>
   </si>
   <si>
     <t>최근게시일</t>
   </si>
   <si>
+    <t>NO</t>
+  </si>
+  <si>
     <t>68.Brazil Receita</t>
   </si>
   <si>
@@ -226,16 +229,16 @@
     <t>22.입법지원센터(정부입법현황)</t>
   </si>
   <si>
-    <t>10.관세법령(행정예고)</t>
-  </si>
-  <si>
-    <t>11.관세법령(최신법령)</t>
-  </si>
-  <si>
-    <t>2.유니패스(행정규칙</t>
-  </si>
-  <si>
-    <t>3.유니패스(판례)</t>
+    <t>4-1.유니패스(행정예고)</t>
+  </si>
+  <si>
+    <t>10.유니패스(최신법령)</t>
+  </si>
+  <si>
+    <t>11.유니패스(행정규칙</t>
+  </si>
+  <si>
+    <t>12.유니패스(판례)</t>
   </si>
   <si>
     <t>4.유니패스(공지사항)</t>
@@ -787,10 +790,19 @@
     <t>customs_tax</t>
   </si>
   <si>
+    <t>SKIP_NEWS_MOVED_TO_STEP2_3</t>
+  </si>
+  <si>
+    <t>CHECK</t>
+  </si>
+  <si>
     <t>OK</t>
   </si>
   <si>
-    <t>CHECK</t>
+    <t>STEP2-3</t>
+  </si>
+  <si>
+    <t>STEP1</t>
   </si>
   <si>
     <t>N</t>
@@ -1151,10 +1163,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:W92"/>
+  <dimension ref="A1:X92"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:23">
+    <row r="1" spans="1:24">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1224,28 +1236,31 @@
       <c r="W1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="2" spans="1:23">
+      <c r="X1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24">
       <c r="A2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="G2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H2">
         <v>5</v>
@@ -1254,54 +1269,60 @@
         <v>1</v>
       </c>
       <c r="J2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K2">
-        <v>1555</v>
+        <v>1795</v>
       </c>
       <c r="L2" s="2">
-        <v>46179.60241898148</v>
+        <v>46242.3665625</v>
       </c>
       <c r="M2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="N2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O2" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="P2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q2" t="s">
-        <v>259</v>
+        <v>265</v>
+      </c>
+      <c r="R2" t="s">
+        <v>263</v>
       </c>
       <c r="W2" s="2">
         <v>46155</v>
       </c>
-    </row>
-    <row r="3" spans="1:23">
+      <c r="X2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24">
       <c r="A3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E3" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="G3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H3">
         <v>5</v>
@@ -1310,54 +1331,60 @@
         <v>1</v>
       </c>
       <c r="J3">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K3">
-        <v>1512</v>
+        <v>1752</v>
       </c>
       <c r="L3" s="2">
-        <v>46179.60244212963</v>
+        <v>46242.3665625</v>
       </c>
       <c r="M3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="N3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O3" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="P3" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q3" t="s">
-        <v>259</v>
+        <v>265</v>
+      </c>
+      <c r="R3" t="s">
+        <v>263</v>
       </c>
       <c r="W3" s="2">
         <v>46087</v>
       </c>
-    </row>
-    <row r="4" spans="1:23">
+      <c r="X3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24">
       <c r="A4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D4" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="G4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H4">
         <v>5</v>
@@ -1366,54 +1393,60 @@
         <v>1</v>
       </c>
       <c r="J4">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K4">
-        <v>1341</v>
+        <v>1533</v>
       </c>
       <c r="L4" s="2">
-        <v>46179.60246527778</v>
+        <v>46242.3665625</v>
       </c>
       <c r="M4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="N4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O4" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="P4" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q4" t="s">
-        <v>259</v>
+        <v>265</v>
+      </c>
+      <c r="R4" t="s">
+        <v>263</v>
       </c>
       <c r="W4" s="2">
         <v>46168</v>
       </c>
-    </row>
-    <row r="5" spans="1:23">
+      <c r="X4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24">
       <c r="A5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C5" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D5" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E5" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F5" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="G5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H5">
         <v>5</v>
@@ -1422,54 +1455,60 @@
         <v>1</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5">
-        <v>297</v>
+        <v>324</v>
       </c>
       <c r="L5" s="2">
-        <v>46179.60246527778</v>
+        <v>46242.3665625</v>
       </c>
       <c r="M5" t="s">
         <v>258</v>
       </c>
       <c r="N5" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O5" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="P5" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q5" t="s">
-        <v>259</v>
+        <v>265</v>
+      </c>
+      <c r="R5" t="s">
+        <v>263</v>
       </c>
       <c r="W5" s="2">
         <v>46161</v>
       </c>
-    </row>
-    <row r="6" spans="1:23">
+      <c r="X5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24">
       <c r="A6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H6">
         <v>5</v>
@@ -1481,51 +1520,57 @@
         <v>1</v>
       </c>
       <c r="K6">
-        <v>101</v>
+        <v>167</v>
       </c>
       <c r="L6" s="2">
-        <v>46179.60248842592</v>
+        <v>46242.36657407408</v>
       </c>
       <c r="M6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="N6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O6" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="P6" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q6" t="s">
-        <v>260</v>
+        <v>266</v>
+      </c>
+      <c r="R6" t="s">
+        <v>264</v>
       </c>
       <c r="W6" s="2">
         <v>46168</v>
       </c>
-    </row>
-    <row r="7" spans="1:23">
+      <c r="X6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24">
       <c r="A7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D7" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E7" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F7" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="G7" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H7">
         <v>5</v>
@@ -1534,54 +1579,60 @@
         <v>1</v>
       </c>
       <c r="J7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="L7" s="2">
-        <v>46179.6025</v>
+        <v>46242.36658564815</v>
       </c>
       <c r="M7" t="s">
         <v>258</v>
       </c>
       <c r="N7" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O7" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="P7" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q7" t="s">
-        <v>259</v>
+        <v>265</v>
+      </c>
+      <c r="R7" t="s">
+        <v>263</v>
       </c>
       <c r="W7" s="2">
         <v>46164</v>
       </c>
-    </row>
-    <row r="8" spans="1:23">
+      <c r="X7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24">
       <c r="A8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C8" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D8" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E8" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F8" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="G8" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H8">
         <v>5</v>
@@ -1590,54 +1641,60 @@
         <v>1</v>
       </c>
       <c r="J8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="L8" s="2">
-        <v>46179.60251157408</v>
+        <v>46242.36658564815</v>
       </c>
       <c r="M8" t="s">
         <v>258</v>
       </c>
       <c r="N8" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O8" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="P8" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q8" t="s">
-        <v>259</v>
+        <v>265</v>
+      </c>
+      <c r="R8" t="s">
+        <v>263</v>
       </c>
       <c r="W8" s="2">
         <v>46155</v>
       </c>
-    </row>
-    <row r="9" spans="1:23">
+      <c r="X8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24">
       <c r="A9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E9" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F9" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="G9" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H9">
         <v>5</v>
@@ -1646,54 +1703,60 @@
         <v>1</v>
       </c>
       <c r="J9">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K9">
-        <v>1690</v>
+        <v>1901</v>
       </c>
       <c r="L9" s="2">
-        <v>46179.60256944445</v>
+        <v>46242.36658564815</v>
       </c>
       <c r="M9" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="N9" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O9" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="P9" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q9" t="s">
-        <v>259</v>
+        <v>265</v>
+      </c>
+      <c r="R9" t="s">
+        <v>263</v>
       </c>
       <c r="W9" s="2">
         <v>46045</v>
       </c>
-    </row>
-    <row r="10" spans="1:23">
+      <c r="X9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24">
       <c r="A10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E10" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="G10" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H10">
         <v>5</v>
@@ -1702,54 +1765,60 @@
         <v>1</v>
       </c>
       <c r="J10">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K10">
-        <v>1493</v>
+        <v>1704</v>
       </c>
       <c r="L10" s="2">
-        <v>46179.60275462963</v>
+        <v>46242.36658564815</v>
       </c>
       <c r="M10" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="N10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O10" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="P10" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q10" t="s">
-        <v>259</v>
+        <v>265</v>
+      </c>
+      <c r="R10" t="s">
+        <v>263</v>
       </c>
       <c r="W10" s="2">
         <v>46045</v>
       </c>
-    </row>
-    <row r="11" spans="1:23">
+      <c r="X10">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24">
       <c r="A11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C11" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D11" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E11" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F11" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="G11" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H11">
         <v>5</v>
@@ -1758,54 +1827,60 @@
         <v>1</v>
       </c>
       <c r="J11">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K11">
-        <v>1464</v>
+        <v>1675</v>
       </c>
       <c r="L11" s="2">
-        <v>46179.60283564815</v>
+        <v>46242.36658564815</v>
       </c>
       <c r="M11" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="N11" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O11" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="P11" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q11" t="s">
-        <v>259</v>
+        <v>265</v>
+      </c>
+      <c r="R11" t="s">
+        <v>263</v>
       </c>
       <c r="W11" s="2">
         <v>46129</v>
       </c>
-    </row>
-    <row r="12" spans="1:23">
+      <c r="X11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24">
       <c r="A12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C12" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D12" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E12" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F12" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="G12" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H12">
         <v>5</v>
@@ -1814,54 +1889,60 @@
         <v>1</v>
       </c>
       <c r="J12">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K12">
-        <v>357</v>
+        <v>405</v>
       </c>
       <c r="L12" s="2">
-        <v>46179.60284722222</v>
+        <v>46242.36658564815</v>
       </c>
       <c r="M12" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="N12" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O12" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="P12" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q12" t="s">
-        <v>259</v>
+        <v>265</v>
+      </c>
+      <c r="R12" t="s">
+        <v>263</v>
       </c>
       <c r="W12" s="2">
         <v>46164</v>
       </c>
-    </row>
-    <row r="13" spans="1:23">
+      <c r="X12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24">
       <c r="A13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C13" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D13" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E13" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F13" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G13" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H13">
         <v>5</v>
@@ -1873,51 +1954,57 @@
         <v>1</v>
       </c>
       <c r="K13">
-        <v>57</v>
+        <v>123</v>
       </c>
       <c r="L13" s="2">
-        <v>46179.60288194445</v>
+        <v>46242.3666087963</v>
       </c>
       <c r="M13" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="N13" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O13" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="P13" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q13" t="s">
-        <v>260</v>
+        <v>266</v>
+      </c>
+      <c r="R13" t="s">
+        <v>264</v>
       </c>
       <c r="W13" s="2">
         <v>46168</v>
       </c>
-    </row>
-    <row r="14" spans="1:23">
+      <c r="X13">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24">
       <c r="A14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C14" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D14" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E14" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F14" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G14" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H14">
         <v>5</v>
@@ -1929,51 +2016,54 @@
         <v>30</v>
       </c>
       <c r="K14">
-        <v>1551</v>
+        <v>3415</v>
       </c>
       <c r="L14" s="2">
-        <v>46179.60290509259</v>
+        <v>46242.36663194445</v>
       </c>
       <c r="M14" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="N14" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O14" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="P14" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q14" t="s">
-        <v>260</v>
+        <v>266</v>
+      </c>
+      <c r="R14" t="s">
+        <v>264</v>
       </c>
       <c r="W14" s="2">
         <v>46168</v>
       </c>
     </row>
-    <row r="15" spans="1:23">
+    <row r="15" spans="1:24">
       <c r="A15" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C15" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D15" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E15" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F15" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G15" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H15">
         <v>5</v>
@@ -1985,51 +2075,54 @@
         <v>30</v>
       </c>
       <c r="K15">
-        <v>1551</v>
+        <v>3415</v>
       </c>
       <c r="L15" s="2">
-        <v>46179.60292824074</v>
+        <v>46242.36665509259</v>
       </c>
       <c r="M15" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="N15" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O15" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="P15" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q15" t="s">
-        <v>260</v>
+        <v>266</v>
+      </c>
+      <c r="R15" t="s">
+        <v>264</v>
       </c>
       <c r="W15" s="2">
         <v>46168</v>
       </c>
     </row>
-    <row r="16" spans="1:23">
+    <row r="16" spans="1:24">
       <c r="A16" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C16" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D16" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E16" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F16" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G16" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H16">
         <v>5</v>
@@ -2041,25 +2134,28 @@
         <v>30</v>
       </c>
       <c r="K16">
-        <v>1551</v>
+        <v>3415</v>
       </c>
       <c r="L16" s="2">
-        <v>46179.60293981482</v>
+        <v>46242.36666666667</v>
       </c>
       <c r="M16" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="N16" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O16" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="P16" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q16" t="s">
-        <v>260</v>
+        <v>266</v>
+      </c>
+      <c r="R16" t="s">
+        <v>264</v>
       </c>
       <c r="W16" s="2">
         <v>46164</v>
@@ -2067,25 +2163,25 @@
     </row>
     <row r="17" spans="1:23">
       <c r="A17" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C17" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D17" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E17" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F17" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="G17" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H17">
         <v>5</v>
@@ -2094,28 +2190,31 @@
         <v>1</v>
       </c>
       <c r="J17">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K17">
-        <v>1569</v>
+        <v>1809</v>
       </c>
       <c r="L17" s="2">
-        <v>46179.60296296296</v>
+        <v>46242.36667824074</v>
       </c>
       <c r="M17" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="N17" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O17" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="P17" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q17" t="s">
-        <v>259</v>
+        <v>265</v>
+      </c>
+      <c r="R17" t="s">
+        <v>263</v>
       </c>
       <c r="W17" s="2">
         <v>46113</v>
@@ -2123,25 +2222,25 @@
     </row>
     <row r="18" spans="1:23">
       <c r="A18" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C18" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D18" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E18" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F18" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G18" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H18">
         <v>5</v>
@@ -2153,25 +2252,28 @@
         <v>30</v>
       </c>
       <c r="K18">
-        <v>1551</v>
+        <v>3531</v>
       </c>
       <c r="L18" s="2">
-        <v>46179.60297453704</v>
+        <v>46242.36667824074</v>
       </c>
       <c r="M18" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="N18" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O18" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="P18" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q18" t="s">
-        <v>260</v>
+        <v>266</v>
+      </c>
+      <c r="R18" t="s">
+        <v>264</v>
       </c>
       <c r="W18" s="2">
         <v>46168</v>
@@ -2179,25 +2281,25 @@
     </row>
     <row r="19" spans="1:23">
       <c r="A19" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C19" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D19" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E19" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F19" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="G19" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H19">
         <v>5</v>
@@ -2206,28 +2308,31 @@
         <v>1</v>
       </c>
       <c r="J19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="L19" s="2">
-        <v>46179.60327546296</v>
+        <v>46242.36668981481</v>
       </c>
       <c r="M19" t="s">
         <v>258</v>
       </c>
       <c r="N19" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O19" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="P19" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q19" t="s">
-        <v>259</v>
+        <v>265</v>
+      </c>
+      <c r="R19" t="s">
+        <v>263</v>
       </c>
       <c r="W19" s="2">
         <v>46163</v>
@@ -2235,25 +2340,25 @@
     </row>
     <row r="20" spans="1:23">
       <c r="A20" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C20" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D20" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E20" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F20" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="G20" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H20">
         <v>5</v>
@@ -2262,28 +2367,31 @@
         <v>1</v>
       </c>
       <c r="J20">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K20">
-        <v>1586</v>
+        <v>1826</v>
       </c>
       <c r="L20" s="2">
-        <v>46179.60329861111</v>
+        <v>46242.36668981481</v>
       </c>
       <c r="M20" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="N20" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O20" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="P20" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q20" t="s">
-        <v>259</v>
+        <v>265</v>
+      </c>
+      <c r="R20" t="s">
+        <v>263</v>
       </c>
       <c r="W20" s="2">
         <v>46165</v>
@@ -2291,25 +2399,25 @@
     </row>
     <row r="21" spans="1:23">
       <c r="A21" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C21" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D21" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E21" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F21" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="G21" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H21">
         <v>5</v>
@@ -2318,28 +2426,31 @@
         <v>1</v>
       </c>
       <c r="J21">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K21">
-        <v>1551</v>
+        <v>1791</v>
       </c>
       <c r="L21" s="2">
-        <v>46179.60331018519</v>
+        <v>46242.36668981481</v>
       </c>
       <c r="M21" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="N21" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O21" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="P21" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q21" t="s">
-        <v>259</v>
+        <v>265</v>
+      </c>
+      <c r="R21" t="s">
+        <v>263</v>
       </c>
       <c r="W21" s="2">
         <v>46166</v>
@@ -2347,25 +2458,25 @@
     </row>
     <row r="22" spans="1:23">
       <c r="A22" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C22" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D22" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E22" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F22" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G22" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H22">
         <v>5</v>
@@ -2377,25 +2488,28 @@
         <v>30</v>
       </c>
       <c r="K22">
-        <v>1551</v>
+        <v>3531</v>
       </c>
       <c r="L22" s="2">
-        <v>46179.60333333333</v>
+        <v>46242.36670138889</v>
       </c>
       <c r="M22" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="N22" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O22" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="P22" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q22" t="s">
-        <v>260</v>
+        <v>266</v>
+      </c>
+      <c r="R22" t="s">
+        <v>264</v>
       </c>
       <c r="W22" s="2">
         <v>46168</v>
@@ -2403,25 +2517,25 @@
     </row>
     <row r="23" spans="1:23">
       <c r="A23" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C23" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D23" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E23" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F23" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G23" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H23">
         <v>5</v>
@@ -2433,25 +2547,28 @@
         <v>30</v>
       </c>
       <c r="K23">
-        <v>1551</v>
+        <v>3531</v>
       </c>
       <c r="L23" s="2">
-        <v>46179.60335648148</v>
+        <v>46242.36671296296</v>
       </c>
       <c r="M23" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="N23" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O23" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="P23" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q23" t="s">
-        <v>260</v>
+        <v>266</v>
+      </c>
+      <c r="R23" t="s">
+        <v>264</v>
       </c>
       <c r="W23" s="2">
         <v>46168</v>
@@ -2459,25 +2576,25 @@
     </row>
     <row r="24" spans="1:23">
       <c r="A24" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C24" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D24" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E24" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F24" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G24" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H24">
         <v>5</v>
@@ -2489,25 +2606,28 @@
         <v>1</v>
       </c>
       <c r="K24">
-        <v>57</v>
+        <v>123</v>
       </c>
       <c r="L24" s="2">
-        <v>46179.60337962963</v>
+        <v>46242.36673611111</v>
       </c>
       <c r="M24" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="N24" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O24" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="P24" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q24" t="s">
-        <v>260</v>
+        <v>266</v>
+      </c>
+      <c r="R24" t="s">
+        <v>264</v>
       </c>
       <c r="W24" s="2">
         <v>46168</v>
@@ -2515,25 +2635,25 @@
     </row>
     <row r="25" spans="1:23">
       <c r="A25" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C25" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D25" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E25" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F25" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G25" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H25">
         <v>5</v>
@@ -2545,25 +2665,28 @@
         <v>1</v>
       </c>
       <c r="K25">
-        <v>57</v>
+        <v>123</v>
       </c>
       <c r="L25" s="2">
-        <v>46179.60341435186</v>
+        <v>46242.36674768518</v>
       </c>
       <c r="M25" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="N25" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O25" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="P25" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q25" t="s">
-        <v>260</v>
+        <v>266</v>
+      </c>
+      <c r="R25" t="s">
+        <v>264</v>
       </c>
       <c r="W25" s="2">
         <v>46167</v>
@@ -2571,25 +2694,25 @@
     </row>
     <row r="26" spans="1:23">
       <c r="A26" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C26" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D26" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E26" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F26" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G26" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H26">
         <v>5</v>
@@ -2601,25 +2724,28 @@
         <v>1</v>
       </c>
       <c r="K26">
-        <v>57</v>
+        <v>123</v>
       </c>
       <c r="L26" s="2">
-        <v>46179.6034375</v>
+        <v>46242.36677083333</v>
       </c>
       <c r="M26" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="N26" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O26" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="P26" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q26" t="s">
-        <v>260</v>
+        <v>266</v>
+      </c>
+      <c r="R26" t="s">
+        <v>264</v>
       </c>
       <c r="W26" s="2">
         <v>46168</v>
@@ -2627,25 +2753,25 @@
     </row>
     <row r="27" spans="1:23">
       <c r="A27" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C27" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D27" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E27" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F27" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="G27" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H27">
         <v>5</v>
@@ -2654,28 +2780,31 @@
         <v>1</v>
       </c>
       <c r="J27">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K27">
-        <v>1926</v>
+        <v>2166</v>
       </c>
       <c r="L27" s="2">
-        <v>46179.60346064815</v>
+        <v>46242.36678240741</v>
       </c>
       <c r="M27" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="N27" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O27" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="P27" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q27" t="s">
-        <v>259</v>
+        <v>265</v>
+      </c>
+      <c r="R27" t="s">
+        <v>263</v>
       </c>
       <c r="W27" s="2">
         <v>46172</v>
@@ -2683,25 +2812,25 @@
     </row>
     <row r="28" spans="1:23">
       <c r="A28" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C28" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D28" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E28" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F28" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="G28" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H28">
         <v>5</v>
@@ -2710,28 +2839,31 @@
         <v>1</v>
       </c>
       <c r="J28">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K28">
-        <v>1964</v>
+        <v>2204</v>
       </c>
       <c r="L28" s="2">
-        <v>46179.60348379629</v>
+        <v>46242.36678240741</v>
       </c>
       <c r="M28" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="N28" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O28" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="P28" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q28" t="s">
-        <v>259</v>
+        <v>265</v>
+      </c>
+      <c r="R28" t="s">
+        <v>263</v>
       </c>
       <c r="W28" s="2">
         <v>46164</v>
@@ -2739,25 +2871,25 @@
     </row>
     <row r="29" spans="1:23">
       <c r="A29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C29" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D29" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E29" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F29" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="G29" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H29">
         <v>5</v>
@@ -2766,28 +2898,31 @@
         <v>1</v>
       </c>
       <c r="J29">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="K29">
-        <v>1565</v>
+        <v>1797</v>
       </c>
       <c r="L29" s="2">
-        <v>46179.60350694445</v>
+        <v>46242.36678240741</v>
       </c>
       <c r="M29" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="N29" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O29" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="P29" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q29" t="s">
-        <v>259</v>
+        <v>265</v>
+      </c>
+      <c r="R29" t="s">
+        <v>263</v>
       </c>
       <c r="W29" s="2">
         <v>46168</v>
@@ -2795,25 +2930,25 @@
     </row>
     <row r="30" spans="1:23">
       <c r="A30" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C30" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D30" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E30" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F30" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="G30" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H30">
         <v>5</v>
@@ -2822,28 +2957,31 @@
         <v>1</v>
       </c>
       <c r="J30">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K30">
-        <v>1161</v>
+        <v>1321</v>
       </c>
       <c r="L30" s="2">
-        <v>46179.60353009259</v>
+        <v>46242.36678240741</v>
       </c>
       <c r="M30" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="N30" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O30" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="P30" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q30" t="s">
-        <v>259</v>
+        <v>265</v>
+      </c>
+      <c r="R30" t="s">
+        <v>263</v>
       </c>
       <c r="W30" s="2">
         <v>46168</v>
@@ -2851,25 +2989,25 @@
     </row>
     <row r="31" spans="1:23">
       <c r="A31" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C31" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D31" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E31" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F31" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="G31" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H31">
         <v>5</v>
@@ -2878,28 +3016,31 @@
         <v>1</v>
       </c>
       <c r="J31">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K31">
-        <v>1141</v>
+        <v>1205</v>
       </c>
       <c r="L31" s="2">
-        <v>46179.60354166666</v>
+        <v>46242.36678240741</v>
       </c>
       <c r="M31" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="N31" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O31" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="P31" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q31" t="s">
-        <v>259</v>
+        <v>265</v>
+      </c>
+      <c r="R31" t="s">
+        <v>263</v>
       </c>
       <c r="W31" s="2">
         <v>46168</v>
@@ -2907,25 +3048,25 @@
     </row>
     <row r="32" spans="1:23">
       <c r="A32" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C32" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D32" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E32" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F32" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G32" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H32">
         <v>5</v>
@@ -2937,25 +3078,28 @@
         <v>1</v>
       </c>
       <c r="K32">
-        <v>3381</v>
+        <v>5441</v>
       </c>
       <c r="L32" s="2">
-        <v>46179.60372685185</v>
+        <v>46242.36688657408</v>
       </c>
       <c r="M32" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="N32" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O32" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="P32" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q32" t="s">
-        <v>260</v>
+        <v>266</v>
+      </c>
+      <c r="R32" t="s">
+        <v>264</v>
       </c>
       <c r="W32" s="2">
         <v>46160</v>
@@ -2963,25 +3107,25 @@
     </row>
     <row r="33" spans="1:23">
       <c r="A33" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C33" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D33" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E33" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F33" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="G33" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H33">
         <v>5</v>
@@ -2990,28 +3134,31 @@
         <v>1</v>
       </c>
       <c r="J33">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K33">
-        <v>440</v>
+        <v>520</v>
       </c>
       <c r="L33" s="2">
-        <v>46179.60376157407</v>
+        <v>46242.36689814815</v>
       </c>
       <c r="M33" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="N33" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O33" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="P33" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q33" t="s">
-        <v>259</v>
+        <v>265</v>
+      </c>
+      <c r="R33" t="s">
+        <v>263</v>
       </c>
       <c r="W33" s="2">
         <v>46168</v>
@@ -3019,25 +3166,25 @@
     </row>
     <row r="34" spans="1:23">
       <c r="A34" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C34" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D34" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E34" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F34" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="G34" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H34">
         <v>5</v>
@@ -3046,28 +3193,31 @@
         <v>1</v>
       </c>
       <c r="J34">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K34">
-        <v>464</v>
+        <v>541</v>
       </c>
       <c r="L34" s="2">
-        <v>46179.60377314815</v>
+        <v>46242.36689814815</v>
       </c>
       <c r="M34" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="N34" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O34" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="P34" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q34" t="s">
-        <v>259</v>
+        <v>265</v>
+      </c>
+      <c r="R34" t="s">
+        <v>263</v>
       </c>
       <c r="W34" s="2">
         <v>46168</v>
@@ -3075,25 +3225,25 @@
     </row>
     <row r="35" spans="1:23">
       <c r="A35" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C35" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D35" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E35" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F35" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G35" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H35">
         <v>5</v>
@@ -3105,25 +3255,28 @@
         <v>30</v>
       </c>
       <c r="K35">
-        <v>1551</v>
+        <v>3531</v>
       </c>
       <c r="L35" s="2">
-        <v>46179.60379629629</v>
+        <v>46242.36690972222</v>
       </c>
       <c r="M35" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="N35" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O35" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="P35" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q35" t="s">
-        <v>260</v>
+        <v>266</v>
+      </c>
+      <c r="R35" t="s">
+        <v>264</v>
       </c>
       <c r="W35" s="2">
         <v>46157</v>
@@ -3131,25 +3284,25 @@
     </row>
     <row r="36" spans="1:23">
       <c r="A36" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C36" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D36" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E36" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F36" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G36" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H36">
         <v>5</v>
@@ -3161,25 +3314,28 @@
         <v>30</v>
       </c>
       <c r="K36">
-        <v>1551</v>
+        <v>3531</v>
       </c>
       <c r="L36" s="2">
-        <v>46179.60381944444</v>
+        <v>46242.3669212963</v>
       </c>
       <c r="M36" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="N36" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O36" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="P36" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q36" t="s">
-        <v>260</v>
+        <v>266</v>
+      </c>
+      <c r="R36" t="s">
+        <v>264</v>
       </c>
       <c r="W36" s="2">
         <v>46168</v>
@@ -3187,25 +3343,25 @@
     </row>
     <row r="37" spans="1:23">
       <c r="A37" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C37" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D37" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E37" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F37" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G37" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H37">
         <v>5</v>
@@ -3214,28 +3370,31 @@
         <v>1</v>
       </c>
       <c r="J37">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="K37">
-        <v>163</v>
+        <v>1766</v>
       </c>
       <c r="L37" s="2">
-        <v>46179.60383101852</v>
+        <v>46242.36694444445</v>
       </c>
       <c r="M37" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="N37" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O37" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="P37" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q37" t="s">
-        <v>260</v>
+        <v>266</v>
+      </c>
+      <c r="R37" t="s">
+        <v>264</v>
       </c>
       <c r="W37" s="2">
         <v>46132</v>
@@ -3243,25 +3402,25 @@
     </row>
     <row r="38" spans="1:23">
       <c r="A38" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C38" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D38" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E38" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F38" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G38" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H38">
         <v>5</v>
@@ -3273,25 +3432,28 @@
         <v>30</v>
       </c>
       <c r="K38">
-        <v>984</v>
+        <v>2877</v>
       </c>
       <c r="L38" s="2">
-        <v>46179.60385416666</v>
+        <v>46242.36695601852</v>
       </c>
       <c r="M38" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="N38" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O38" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="P38" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q38" t="s">
-        <v>260</v>
+        <v>266</v>
+      </c>
+      <c r="R38" t="s">
+        <v>264</v>
       </c>
       <c r="W38" s="2">
         <v>46113</v>
@@ -3299,25 +3461,25 @@
     </row>
     <row r="39" spans="1:23">
       <c r="A39" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C39" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D39" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E39" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F39" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G39" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H39">
         <v>5</v>
@@ -3329,25 +3491,28 @@
         <v>30</v>
       </c>
       <c r="K39">
-        <v>1252</v>
+        <v>3116</v>
       </c>
       <c r="L39" s="2">
-        <v>46179.60386574074</v>
+        <v>46242.36696759259</v>
       </c>
       <c r="M39" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="N39" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O39" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="P39" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q39" t="s">
-        <v>260</v>
+        <v>266</v>
+      </c>
+      <c r="R39" t="s">
+        <v>264</v>
       </c>
       <c r="W39" s="2">
         <v>46140</v>
@@ -3355,25 +3520,25 @@
     </row>
     <row r="40" spans="1:23">
       <c r="A40" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C40" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D40" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E40" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F40" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G40" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H40">
         <v>5</v>
@@ -3385,25 +3550,28 @@
         <v>30</v>
       </c>
       <c r="K40">
-        <v>1262</v>
+        <v>3068</v>
       </c>
       <c r="L40" s="2">
-        <v>46179.60388888889</v>
+        <v>46242.36697916667</v>
       </c>
       <c r="M40" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="N40" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O40" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="P40" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q40" t="s">
-        <v>260</v>
+        <v>266</v>
+      </c>
+      <c r="R40" t="s">
+        <v>264</v>
       </c>
       <c r="W40" s="2">
         <v>46024</v>
@@ -3411,25 +3579,25 @@
     </row>
     <row r="41" spans="1:23">
       <c r="A41" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C41" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D41" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E41" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F41" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G41" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H41">
         <v>5</v>
@@ -3441,25 +3609,28 @@
         <v>30</v>
       </c>
       <c r="K41">
-        <v>1531</v>
+        <v>3482</v>
       </c>
       <c r="L41" s="2">
-        <v>46179.60390046296</v>
+        <v>46242.36700231482</v>
       </c>
       <c r="M41" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="N41" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O41" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="P41" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q41" t="s">
-        <v>260</v>
+        <v>266</v>
+      </c>
+      <c r="R41" t="s">
+        <v>264</v>
       </c>
       <c r="W41" s="2">
         <v>46168</v>
@@ -3467,25 +3638,25 @@
     </row>
     <row r="42" spans="1:23">
       <c r="A42" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C42" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D42" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E42" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F42" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G42" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H42">
         <v>5</v>
@@ -3497,25 +3668,28 @@
         <v>30</v>
       </c>
       <c r="K42">
-        <v>1493</v>
+        <v>3473</v>
       </c>
       <c r="L42" s="2">
-        <v>46179.60391203704</v>
+        <v>46242.36701388889</v>
       </c>
       <c r="M42" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="N42" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O42" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="P42" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q42" t="s">
-        <v>260</v>
+        <v>266</v>
+      </c>
+      <c r="R42" t="s">
+        <v>264</v>
       </c>
       <c r="W42" s="2">
         <v>46164</v>
@@ -3523,25 +3697,25 @@
     </row>
     <row r="43" spans="1:23">
       <c r="A43" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C43" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D43" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E43" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F43" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G43" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H43">
         <v>5</v>
@@ -3553,25 +3727,28 @@
         <v>30</v>
       </c>
       <c r="K43">
-        <v>1473</v>
+        <v>3453</v>
       </c>
       <c r="L43" s="2">
-        <v>46179.60392361111</v>
+        <v>46242.36702546296</v>
       </c>
       <c r="M43" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="N43" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O43" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="P43" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q43" t="s">
-        <v>260</v>
+        <v>266</v>
+      </c>
+      <c r="R43" t="s">
+        <v>264</v>
       </c>
       <c r="W43" s="2">
         <v>46112</v>
@@ -3579,25 +3756,25 @@
     </row>
     <row r="44" spans="1:23">
       <c r="A44" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C44" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D44" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E44" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F44" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="G44" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H44">
         <v>5</v>
@@ -3606,28 +3783,31 @@
         <v>1</v>
       </c>
       <c r="J44">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K44">
-        <v>1028</v>
+        <v>1124</v>
       </c>
       <c r="L44" s="2">
-        <v>46179.60394675926</v>
+        <v>46242.36702546296</v>
       </c>
       <c r="M44" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="N44" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O44" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="P44" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q44" t="s">
-        <v>259</v>
+        <v>265</v>
+      </c>
+      <c r="R44" t="s">
+        <v>263</v>
       </c>
       <c r="W44" s="2">
         <v>46171</v>
@@ -3635,25 +3815,25 @@
     </row>
     <row r="45" spans="1:23">
       <c r="A45" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C45" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D45" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E45" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F45" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G45" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H45">
         <v>5</v>
@@ -3665,25 +3845,28 @@
         <v>20</v>
       </c>
       <c r="K45">
-        <v>1476</v>
+        <v>2780</v>
       </c>
       <c r="L45" s="2">
-        <v>46179.60395833333</v>
+        <v>46242.36703703704</v>
       </c>
       <c r="M45" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="N45" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O45" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="P45" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q45" t="s">
-        <v>260</v>
+        <v>266</v>
+      </c>
+      <c r="R45" t="s">
+        <v>264</v>
       </c>
       <c r="W45" s="2">
         <v>46168</v>
@@ -3691,25 +3874,25 @@
     </row>
     <row r="46" spans="1:23">
       <c r="A46" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C46" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D46" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E46" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F46" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G46" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H46">
         <v>5</v>
@@ -3721,25 +3904,28 @@
         <v>20</v>
       </c>
       <c r="K46">
-        <v>1641</v>
+        <v>2957</v>
       </c>
       <c r="L46" s="2">
-        <v>46179.60398148148</v>
+        <v>46242.36706018518</v>
       </c>
       <c r="M46" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="N46" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O46" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="P46" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q46" t="s">
-        <v>260</v>
+        <v>266</v>
+      </c>
+      <c r="R46" t="s">
+        <v>264</v>
       </c>
       <c r="W46" s="2">
         <v>46168</v>
@@ -3747,25 +3933,25 @@
     </row>
     <row r="47" spans="1:23">
       <c r="A47" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C47" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D47" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E47" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F47" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G47" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H47">
         <v>5</v>
@@ -3777,25 +3963,28 @@
         <v>20</v>
       </c>
       <c r="K47">
-        <v>1682</v>
+        <v>3012</v>
       </c>
       <c r="L47" s="2">
-        <v>46179.60400462963</v>
+        <v>46242.36708333333</v>
       </c>
       <c r="M47" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="N47" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O47" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="P47" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q47" t="s">
-        <v>260</v>
+        <v>266</v>
+      </c>
+      <c r="R47" t="s">
+        <v>264</v>
       </c>
       <c r="W47" s="2">
         <v>46168</v>
@@ -3803,25 +3992,25 @@
     </row>
     <row r="48" spans="1:23">
       <c r="A48" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C48" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D48" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E48" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F48" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G48" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H48">
         <v>5</v>
@@ -3830,28 +4019,31 @@
         <v>1</v>
       </c>
       <c r="J48">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K48">
-        <v>1035</v>
+        <v>2259</v>
       </c>
       <c r="L48" s="2">
-        <v>46179.60402777778</v>
+        <v>46242.36709490741</v>
       </c>
       <c r="M48" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="N48" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O48" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="P48" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q48" t="s">
-        <v>260</v>
+        <v>266</v>
+      </c>
+      <c r="R48" t="s">
+        <v>264</v>
       </c>
       <c r="W48" s="2">
         <v>46168</v>
@@ -3859,25 +4051,25 @@
     </row>
     <row r="49" spans="1:23">
       <c r="A49" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C49" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D49" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E49" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F49" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G49" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H49">
         <v>5</v>
@@ -3889,25 +4081,28 @@
         <v>10</v>
       </c>
       <c r="K49">
-        <v>793</v>
+        <v>1453</v>
       </c>
       <c r="L49" s="2">
-        <v>46179.60416666666</v>
+        <v>46242.36721064815</v>
       </c>
       <c r="M49" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="N49" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O49" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="P49" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q49" t="s">
-        <v>260</v>
+        <v>266</v>
+      </c>
+      <c r="R49" t="s">
+        <v>264</v>
       </c>
       <c r="W49" s="2">
         <v>46163</v>
@@ -3915,25 +4110,25 @@
     </row>
     <row r="50" spans="1:23">
       <c r="A50" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C50" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D50" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E50" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F50" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G50" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H50">
         <v>5</v>
@@ -3945,25 +4140,28 @@
         <v>10</v>
       </c>
       <c r="K50">
-        <v>802</v>
+        <v>1453</v>
       </c>
       <c r="L50" s="2">
-        <v>46179.60428240741</v>
+        <v>46242.36731481482</v>
       </c>
       <c r="M50" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="N50" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O50" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="P50" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q50" t="s">
-        <v>260</v>
+        <v>266</v>
+      </c>
+      <c r="R50" t="s">
+        <v>264</v>
       </c>
       <c r="W50" s="2">
         <v>46164</v>
@@ -3971,25 +4169,25 @@
     </row>
     <row r="51" spans="1:23">
       <c r="A51" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C51" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D51" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E51" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F51" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G51" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H51">
         <v>5</v>
@@ -4001,25 +4199,28 @@
         <v>10</v>
       </c>
       <c r="K51">
-        <v>802</v>
+        <v>1444</v>
       </c>
       <c r="L51" s="2">
-        <v>46179.60440972223</v>
+        <v>46242.36746527778</v>
       </c>
       <c r="M51" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="N51" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O51" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="P51" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q51" t="s">
-        <v>260</v>
+        <v>266</v>
+      </c>
+      <c r="R51" t="s">
+        <v>264</v>
       </c>
       <c r="W51" s="2">
         <v>46160</v>
@@ -4027,25 +4228,25 @@
     </row>
     <row r="52" spans="1:23">
       <c r="A52" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C52" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D52" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E52" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F52" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G52" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H52">
         <v>5</v>
@@ -4057,25 +4258,28 @@
         <v>10</v>
       </c>
       <c r="K52">
-        <v>786</v>
+        <v>1446</v>
       </c>
       <c r="L52" s="2">
-        <v>46179.60453703703</v>
+        <v>46242.36758101852</v>
       </c>
       <c r="M52" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="N52" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O52" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="P52" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q52" t="s">
-        <v>260</v>
+        <v>266</v>
+      </c>
+      <c r="R52" t="s">
+        <v>264</v>
       </c>
       <c r="W52" s="2">
         <v>46142</v>
@@ -4083,25 +4287,25 @@
     </row>
     <row r="53" spans="1:23">
       <c r="A53" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C53" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D53" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E53" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F53" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G53" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H53">
         <v>5</v>
@@ -4113,25 +4317,28 @@
         <v>15</v>
       </c>
       <c r="K53">
-        <v>876</v>
+        <v>1890</v>
       </c>
       <c r="L53" s="2">
-        <v>46179.60471064815</v>
+        <v>46242.36770833333</v>
       </c>
       <c r="M53" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="N53" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O53" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="P53" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q53" t="s">
-        <v>260</v>
+        <v>266</v>
+      </c>
+      <c r="R53" t="s">
+        <v>264</v>
       </c>
       <c r="W53" s="2">
         <v>46168</v>
@@ -4139,25 +4346,25 @@
     </row>
     <row r="54" spans="1:23">
       <c r="A54" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C54" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D54" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E54" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F54" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G54" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H54">
         <v>5</v>
@@ -4169,25 +4376,28 @@
         <v>10</v>
       </c>
       <c r="K54">
-        <v>631</v>
+        <v>1291</v>
       </c>
       <c r="L54" s="2">
-        <v>46179.6047337963</v>
+        <v>46242.36771990741</v>
       </c>
       <c r="M54" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="N54" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O54" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="P54" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q54" t="s">
-        <v>260</v>
+        <v>266</v>
+      </c>
+      <c r="R54" t="s">
+        <v>264</v>
       </c>
       <c r="W54" s="2">
         <v>46163</v>
@@ -4195,25 +4405,25 @@
     </row>
     <row r="55" spans="1:23">
       <c r="A55" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C55" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D55" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E55" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F55" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G55" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H55">
         <v>5</v>
@@ -4225,25 +4435,28 @@
         <v>10</v>
       </c>
       <c r="K55">
-        <v>838</v>
+        <v>1498</v>
       </c>
       <c r="L55" s="2">
-        <v>46179.60476851852</v>
+        <v>46242.36775462963</v>
       </c>
       <c r="M55" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="N55" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O55" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="P55" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q55" t="s">
-        <v>260</v>
+        <v>266</v>
+      </c>
+      <c r="R55" t="s">
+        <v>264</v>
       </c>
       <c r="W55" s="2">
         <v>46168</v>
@@ -4251,25 +4464,25 @@
     </row>
     <row r="56" spans="1:23">
       <c r="A56" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C56" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D56" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E56" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F56" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="G56" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H56">
         <v>5</v>
@@ -4278,28 +4491,31 @@
         <v>1</v>
       </c>
       <c r="J56">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K56">
-        <v>589</v>
+        <v>661</v>
       </c>
       <c r="L56" s="2">
-        <v>46179.60479166666</v>
+        <v>46242.3677662037</v>
       </c>
       <c r="M56" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="N56" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O56" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="P56" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q56" t="s">
-        <v>259</v>
+        <v>265</v>
+      </c>
+      <c r="R56" t="s">
+        <v>263</v>
       </c>
       <c r="W56" s="2">
         <v>46161</v>
@@ -4307,25 +4523,25 @@
     </row>
     <row r="57" spans="1:23">
       <c r="A57" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C57" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D57" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E57" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F57" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G57" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H57">
         <v>5</v>
@@ -4337,25 +4553,28 @@
         <v>30</v>
       </c>
       <c r="K57">
-        <v>1662</v>
+        <v>3642</v>
       </c>
       <c r="L57" s="2">
-        <v>46179.60481481482</v>
+        <v>46242.3677662037</v>
       </c>
       <c r="M57" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="N57" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O57" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="P57" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q57" t="s">
-        <v>260</v>
+        <v>266</v>
+      </c>
+      <c r="R57" t="s">
+        <v>264</v>
       </c>
       <c r="W57" s="2">
         <v>46164</v>
@@ -4363,25 +4582,25 @@
     </row>
     <row r="58" spans="1:23">
       <c r="A58" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C58" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D58" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E58" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F58" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="G58" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H58">
         <v>5</v>
@@ -4390,28 +4609,31 @@
         <v>1</v>
       </c>
       <c r="J58">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K58">
-        <v>902</v>
+        <v>982</v>
       </c>
       <c r="L58" s="2">
-        <v>46179.60482638889</v>
+        <v>46242.36777777778</v>
       </c>
       <c r="M58" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="N58" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O58" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="P58" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q58" t="s">
-        <v>259</v>
+        <v>265</v>
+      </c>
+      <c r="R58" t="s">
+        <v>263</v>
       </c>
       <c r="W58" s="2">
         <v>46148</v>
@@ -4419,25 +4641,25 @@
     </row>
     <row r="59" spans="1:23">
       <c r="A59" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C59" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D59" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E59" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F59" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="G59" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H59">
         <v>5</v>
@@ -4446,28 +4668,31 @@
         <v>1</v>
       </c>
       <c r="J59">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K59">
-        <v>910</v>
+        <v>982</v>
       </c>
       <c r="L59" s="2">
-        <v>46179.60483796296</v>
+        <v>46242.36777777778</v>
       </c>
       <c r="M59" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="N59" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O59" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="P59" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q59" t="s">
-        <v>259</v>
+        <v>265</v>
+      </c>
+      <c r="R59" t="s">
+        <v>263</v>
       </c>
       <c r="W59" s="2">
         <v>46168</v>
@@ -4475,25 +4700,25 @@
     </row>
     <row r="60" spans="1:23">
       <c r="A60" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C60" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D60" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E60" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F60" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="G60" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H60">
         <v>5</v>
@@ -4502,28 +4727,31 @@
         <v>1</v>
       </c>
       <c r="J60">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K60">
-        <v>806</v>
+        <v>886</v>
       </c>
       <c r="L60" s="2">
-        <v>46179.60484953703</v>
+        <v>46242.36777777778</v>
       </c>
       <c r="M60" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="N60" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O60" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="P60" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q60" t="s">
-        <v>259</v>
+        <v>265</v>
+      </c>
+      <c r="R60" t="s">
+        <v>263</v>
       </c>
       <c r="W60" s="2">
         <v>46164</v>
@@ -4531,25 +4759,25 @@
     </row>
     <row r="61" spans="1:23">
       <c r="A61" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C61" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D61" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E61" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F61" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="G61" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H61">
         <v>5</v>
@@ -4558,28 +4786,31 @@
         <v>1</v>
       </c>
       <c r="J61">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K61">
-        <v>940</v>
+        <v>1020</v>
       </c>
       <c r="L61" s="2">
-        <v>46179.60484953703</v>
+        <v>46242.36777777778</v>
       </c>
       <c r="M61" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="N61" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O61" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="P61" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q61" t="s">
-        <v>259</v>
+        <v>265</v>
+      </c>
+      <c r="R61" t="s">
+        <v>263</v>
       </c>
       <c r="W61" s="2">
         <v>46168</v>
@@ -4587,25 +4818,25 @@
     </row>
     <row r="62" spans="1:23">
       <c r="A62" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C62" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D62" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E62" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F62" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G62" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H62">
         <v>5</v>
@@ -4617,25 +4848,28 @@
         <v>10</v>
       </c>
       <c r="K62">
-        <v>940</v>
+        <v>1600</v>
       </c>
       <c r="L62" s="2">
-        <v>46179.60486111111</v>
+        <v>46242.36777777778</v>
       </c>
       <c r="M62" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="N62" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O62" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="P62" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q62" t="s">
-        <v>260</v>
+        <v>266</v>
+      </c>
+      <c r="R62" t="s">
+        <v>264</v>
       </c>
       <c r="W62" s="2">
         <v>46164</v>
@@ -4643,25 +4877,25 @@
     </row>
     <row r="63" spans="1:23">
       <c r="A63" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C63" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D63" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E63" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F63" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="G63" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H63">
         <v>5</v>
@@ -4670,28 +4904,31 @@
         <v>1</v>
       </c>
       <c r="J63">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K63">
-        <v>1765</v>
+        <v>2005</v>
       </c>
       <c r="L63" s="2">
-        <v>46179.60488425926</v>
+        <v>46242.36778935185</v>
       </c>
       <c r="M63" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="N63" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O63" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="P63" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q63" t="s">
-        <v>259</v>
+        <v>265</v>
+      </c>
+      <c r="R63" t="s">
+        <v>263</v>
       </c>
       <c r="W63" s="2">
         <v>46164</v>
@@ -4699,25 +4936,25 @@
     </row>
     <row r="64" spans="1:23">
       <c r="A64" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C64" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D64" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E64" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F64" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="G64" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H64">
         <v>5</v>
@@ -4726,13 +4963,13 @@
         <v>1</v>
       </c>
       <c r="J64">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K64">
-        <v>343</v>
+        <v>958</v>
       </c>
       <c r="L64" s="2">
-        <v>46179.60490740741</v>
+        <v>46242.36778935185</v>
       </c>
       <c r="M64" t="s">
         <v>258</v>
@@ -4741,13 +4978,16 @@
         <v>253</v>
       </c>
       <c r="O64" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="P64" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q64" t="s">
-        <v>260</v>
+        <v>266</v>
+      </c>
+      <c r="R64" t="s">
+        <v>264</v>
       </c>
       <c r="W64" s="2">
         <v>46168</v>
@@ -4755,25 +4995,25 @@
     </row>
     <row r="65" spans="1:23">
       <c r="A65" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C65" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D65" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E65" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F65" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G65" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H65">
         <v>5</v>
@@ -4785,25 +5025,28 @@
         <v>30</v>
       </c>
       <c r="K65">
-        <v>992</v>
+        <v>2943</v>
       </c>
       <c r="L65" s="2">
-        <v>46179.60502314815</v>
+        <v>46242.36790509259</v>
       </c>
       <c r="M65" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="N65" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O65" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="P65" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q65" t="s">
-        <v>260</v>
+        <v>266</v>
+      </c>
+      <c r="R65" t="s">
+        <v>264</v>
       </c>
       <c r="W65" s="2">
         <v>46168</v>
@@ -4811,25 +5054,25 @@
     </row>
     <row r="66" spans="1:23">
       <c r="A66" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C66" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D66" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E66" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F66" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G66" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H66">
         <v>5</v>
@@ -4841,25 +5084,28 @@
         <v>30</v>
       </c>
       <c r="K66">
-        <v>997</v>
+        <v>2977</v>
       </c>
       <c r="L66" s="2">
-        <v>46179.60519675926</v>
+        <v>46242.36804398148</v>
       </c>
       <c r="M66" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="N66" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O66" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="P66" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q66" t="s">
-        <v>260</v>
+        <v>266</v>
+      </c>
+      <c r="R66" t="s">
+        <v>264</v>
       </c>
       <c r="W66" s="2">
         <v>46160</v>
@@ -4867,25 +5113,25 @@
     </row>
     <row r="67" spans="1:23">
       <c r="A67" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C67" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D67" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E67" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F67" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G67" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H67">
         <v>5</v>
@@ -4894,28 +5140,31 @@
         <v>1</v>
       </c>
       <c r="J67">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="K67">
-        <v>750</v>
+        <v>1570</v>
       </c>
       <c r="L67" s="2">
-        <v>46179.60520833333</v>
+        <v>46242.36806712963</v>
       </c>
       <c r="M67" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="N67" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O67" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="P67" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q67" t="s">
-        <v>260</v>
+        <v>266</v>
+      </c>
+      <c r="R67" t="s">
+        <v>264</v>
       </c>
       <c r="W67" s="2">
         <v>46168</v>
@@ -4923,25 +5172,25 @@
     </row>
     <row r="68" spans="1:23">
       <c r="A68" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C68" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D68" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E68" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F68" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G68" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H68">
         <v>5</v>
@@ -4953,25 +5202,28 @@
         <v>30</v>
       </c>
       <c r="K68">
-        <v>1006</v>
+        <v>2957</v>
       </c>
       <c r="L68" s="2">
-        <v>46179.60532407407</v>
+        <v>46242.36819444445</v>
       </c>
       <c r="M68" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="N68" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O68" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="P68" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q68" t="s">
-        <v>260</v>
+        <v>266</v>
+      </c>
+      <c r="R68" t="s">
+        <v>264</v>
       </c>
       <c r="W68" s="2">
         <v>46168</v>
@@ -4979,25 +5231,25 @@
     </row>
     <row r="69" spans="1:23">
       <c r="A69" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C69" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D69" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E69" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F69" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G69" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H69">
         <v>5</v>
@@ -5009,25 +5261,28 @@
         <v>30</v>
       </c>
       <c r="K69">
-        <v>1006</v>
+        <v>2986</v>
       </c>
       <c r="L69" s="2">
-        <v>46179.60547453703</v>
+        <v>46242.36833333333</v>
       </c>
       <c r="M69" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="N69" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O69" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="P69" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q69" t="s">
-        <v>260</v>
+        <v>266</v>
+      </c>
+      <c r="R69" t="s">
+        <v>264</v>
       </c>
       <c r="W69" s="2">
         <v>46168</v>
@@ -5035,25 +5290,25 @@
     </row>
     <row r="70" spans="1:23">
       <c r="A70" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C70" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D70" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E70" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F70" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G70" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H70">
         <v>5</v>
@@ -5062,28 +5317,31 @@
         <v>1</v>
       </c>
       <c r="J70">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K70">
-        <v>1031</v>
+        <v>1940</v>
       </c>
       <c r="L70" s="2">
-        <v>46179.60548611111</v>
+        <v>46242.36834490741</v>
       </c>
       <c r="M70" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="N70" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O70" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="P70" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q70" t="s">
-        <v>260</v>
+        <v>266</v>
+      </c>
+      <c r="R70" t="s">
+        <v>264</v>
       </c>
       <c r="W70" s="2">
         <v>46168</v>
@@ -5091,25 +5349,25 @@
     </row>
     <row r="71" spans="1:23">
       <c r="A71" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C71" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D71" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E71" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F71" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G71" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H71">
         <v>5</v>
@@ -5118,28 +5376,31 @@
         <v>1</v>
       </c>
       <c r="J71">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K71">
-        <v>1028</v>
+        <v>1904</v>
       </c>
       <c r="L71" s="2">
-        <v>46179.60549768519</v>
+        <v>46242.36835648148</v>
       </c>
       <c r="M71" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="N71" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O71" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="P71" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q71" t="s">
-        <v>260</v>
+        <v>266</v>
+      </c>
+      <c r="R71" t="s">
+        <v>264</v>
       </c>
       <c r="W71" s="2">
         <v>46168</v>
@@ -5147,25 +5408,25 @@
     </row>
     <row r="72" spans="1:23">
       <c r="A72" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C72" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D72" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E72" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F72" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="G72" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H72">
         <v>5</v>
@@ -5174,28 +5435,31 @@
         <v>1</v>
       </c>
       <c r="J72">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K72">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="L72" s="2">
-        <v>46179.60550925926</v>
+        <v>46242.36836805556</v>
       </c>
       <c r="M72" t="s">
         <v>258</v>
       </c>
       <c r="N72" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O72" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="P72" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q72" t="s">
-        <v>259</v>
+        <v>265</v>
+      </c>
+      <c r="R72" t="s">
+        <v>263</v>
       </c>
       <c r="W72" s="2">
         <v>46164</v>
@@ -5203,25 +5467,25 @@
     </row>
     <row r="73" spans="1:23">
       <c r="A73" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C73" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D73" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E73" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F73" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G73" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H73">
         <v>5</v>
@@ -5233,25 +5497,28 @@
         <v>12</v>
       </c>
       <c r="K73">
-        <v>581</v>
+        <v>1241</v>
       </c>
       <c r="L73" s="2">
-        <v>46179.6055324074</v>
+        <v>46242.36836805556</v>
       </c>
       <c r="M73" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="N73" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O73" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="P73" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q73" t="s">
-        <v>260</v>
+        <v>266</v>
+      </c>
+      <c r="R73" t="s">
+        <v>264</v>
       </c>
       <c r="W73" s="2">
         <v>46164</v>
@@ -5259,25 +5526,25 @@
     </row>
     <row r="74" spans="1:23">
       <c r="A74" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C74" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D74" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E74" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F74" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G74" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H74">
         <v>5</v>
@@ -5286,28 +5553,31 @@
         <v>1</v>
       </c>
       <c r="J74">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K74">
-        <v>666</v>
+        <v>1425</v>
       </c>
       <c r="L74" s="2">
-        <v>46179.60554398148</v>
+        <v>46242.3683912037</v>
       </c>
       <c r="M74" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="N74" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O74" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="P74" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q74" t="s">
-        <v>260</v>
+        <v>266</v>
+      </c>
+      <c r="R74" t="s">
+        <v>264</v>
       </c>
       <c r="W74" s="2">
         <v>46185</v>
@@ -5315,25 +5585,25 @@
     </row>
     <row r="75" spans="1:23">
       <c r="A75" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C75" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D75" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E75" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F75" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G75" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H75">
         <v>5</v>
@@ -5345,25 +5615,28 @@
         <v>12</v>
       </c>
       <c r="K75">
-        <v>675</v>
+        <v>1456</v>
       </c>
       <c r="L75" s="2">
-        <v>46179.60556712963</v>
+        <v>46242.36840277778</v>
       </c>
       <c r="M75" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="N75" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O75" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="P75" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q75" t="s">
-        <v>260</v>
+        <v>266</v>
+      </c>
+      <c r="R75" t="s">
+        <v>264</v>
       </c>
       <c r="W75" s="2">
         <v>46149</v>
@@ -5371,25 +5644,25 @@
     </row>
     <row r="76" spans="1:23">
       <c r="A76" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C76" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D76" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E76" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F76" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G76" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H76">
         <v>5</v>
@@ -5401,25 +5674,28 @@
         <v>12</v>
       </c>
       <c r="K76">
-        <v>719</v>
+        <v>1500</v>
       </c>
       <c r="L76" s="2">
-        <v>46179.60559027778</v>
+        <v>46242.36842592592</v>
       </c>
       <c r="M76" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="N76" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O76" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="P76" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q76" t="s">
-        <v>260</v>
+        <v>266</v>
+      </c>
+      <c r="R76" t="s">
+        <v>264</v>
       </c>
       <c r="W76" s="2">
         <v>46149</v>
@@ -5427,25 +5703,25 @@
     </row>
     <row r="77" spans="1:23">
       <c r="A77" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C77" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D77" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E77" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F77" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G77" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H77">
         <v>5</v>
@@ -5457,25 +5733,28 @@
         <v>12</v>
       </c>
       <c r="K77">
-        <v>721</v>
+        <v>1513</v>
       </c>
       <c r="L77" s="2">
-        <v>46179.60561342593</v>
+        <v>46242.3684375</v>
       </c>
       <c r="M77" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="N77" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O77" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="P77" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q77" t="s">
-        <v>260</v>
+        <v>266</v>
+      </c>
+      <c r="R77" t="s">
+        <v>264</v>
       </c>
       <c r="W77" s="2">
         <v>46168</v>
@@ -5483,25 +5762,25 @@
     </row>
     <row r="78" spans="1:23">
       <c r="A78" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C78" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D78" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E78" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F78" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G78" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H78">
         <v>5</v>
@@ -5513,25 +5792,28 @@
         <v>12</v>
       </c>
       <c r="K78">
-        <v>732</v>
+        <v>1513</v>
       </c>
       <c r="L78" s="2">
-        <v>46179.605625</v>
+        <v>46242.36846064815</v>
       </c>
       <c r="M78" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="N78" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O78" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="P78" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q78" t="s">
-        <v>260</v>
+        <v>266</v>
+      </c>
+      <c r="R78" t="s">
+        <v>264</v>
       </c>
       <c r="W78" s="2">
         <v>46160</v>
@@ -5539,25 +5821,25 @@
     </row>
     <row r="79" spans="1:23">
       <c r="A79" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C79" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D79" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E79" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F79" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G79" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H79">
         <v>5</v>
@@ -5569,25 +5851,28 @@
         <v>12</v>
       </c>
       <c r="K79">
-        <v>734</v>
+        <v>1526</v>
       </c>
       <c r="L79" s="2">
-        <v>46179.60564814815</v>
+        <v>46242.36847222222</v>
       </c>
       <c r="M79" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="N79" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O79" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="P79" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q79" t="s">
-        <v>260</v>
+        <v>266</v>
+      </c>
+      <c r="R79" t="s">
+        <v>264</v>
       </c>
       <c r="W79" s="2">
         <v>46168</v>
@@ -5595,25 +5880,25 @@
     </row>
     <row r="80" spans="1:23">
       <c r="A80" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C80" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D80" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E80" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F80" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G80" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H80">
         <v>5</v>
@@ -5625,25 +5910,28 @@
         <v>10</v>
       </c>
       <c r="K80">
-        <v>665</v>
+        <v>1325</v>
       </c>
       <c r="L80" s="2">
-        <v>46179.60565972222</v>
+        <v>46242.36848379629</v>
       </c>
       <c r="M80" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="N80" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O80" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="P80" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q80" t="s">
-        <v>260</v>
+        <v>266</v>
+      </c>
+      <c r="R80" t="s">
+        <v>264</v>
       </c>
       <c r="W80" s="2">
         <v>46164</v>
@@ -5651,25 +5939,25 @@
     </row>
     <row r="81" spans="1:23">
       <c r="A81" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C81" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D81" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E81" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F81" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G81" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H81">
         <v>5</v>
@@ -5681,25 +5969,28 @@
         <v>30</v>
       </c>
       <c r="K81">
-        <v>1551</v>
+        <v>3531</v>
       </c>
       <c r="L81" s="2">
-        <v>46179.60568287037</v>
+        <v>46242.36850694445</v>
       </c>
       <c r="M81" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="N81" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O81" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="P81" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q81" t="s">
-        <v>260</v>
+        <v>266</v>
+      </c>
+      <c r="R81" t="s">
+        <v>264</v>
       </c>
       <c r="W81" s="2">
         <v>46160</v>
@@ -5707,25 +5998,25 @@
     </row>
     <row r="82" spans="1:23">
       <c r="A82" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C82" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D82" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E82" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F82" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="G82" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H82">
         <v>5</v>
@@ -5734,28 +6025,31 @@
         <v>1</v>
       </c>
       <c r="J82">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K82">
-        <v>1837</v>
+        <v>2077</v>
       </c>
       <c r="L82" s="2">
-        <v>46179.60570601852</v>
+        <v>46242.36850694445</v>
       </c>
       <c r="M82" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="N82" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O82" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="P82" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q82" t="s">
-        <v>259</v>
+        <v>265</v>
+      </c>
+      <c r="R82" t="s">
+        <v>263</v>
       </c>
       <c r="W82" s="2">
         <v>46161</v>
@@ -5763,25 +6057,25 @@
     </row>
     <row r="83" spans="1:23">
       <c r="A83" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C83" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D83" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E83" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F83" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="G83" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H83">
         <v>5</v>
@@ -5790,28 +6084,31 @@
         <v>1</v>
       </c>
       <c r="J83">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K83">
-        <v>436</v>
+        <v>476</v>
       </c>
       <c r="L83" s="2">
-        <v>46179.6057175926</v>
+        <v>46242.36850694445</v>
       </c>
       <c r="M83" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="N83" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O83" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="P83" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q83" t="s">
-        <v>259</v>
+        <v>265</v>
+      </c>
+      <c r="R83" t="s">
+        <v>263</v>
       </c>
       <c r="W83" s="2">
         <v>46168</v>
@@ -5819,25 +6116,25 @@
     </row>
     <row r="84" spans="1:23">
       <c r="A84" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C84" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D84" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E84" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F84" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="G84" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H84">
         <v>5</v>
@@ -5846,28 +6143,31 @@
         <v>1</v>
       </c>
       <c r="J84">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K84">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="L84" s="2">
-        <v>46179.60574074074</v>
+        <v>46242.36850694445</v>
       </c>
       <c r="M84" t="s">
         <v>258</v>
       </c>
       <c r="N84" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O84" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="P84" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q84" t="s">
-        <v>259</v>
+        <v>265</v>
+      </c>
+      <c r="R84" t="s">
+        <v>263</v>
       </c>
       <c r="W84" s="2">
         <v>46164</v>
@@ -5875,25 +6175,25 @@
     </row>
     <row r="85" spans="1:23">
       <c r="A85" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C85" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D85" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E85" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F85" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="G85" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H85">
         <v>5</v>
@@ -5902,28 +6202,31 @@
         <v>1</v>
       </c>
       <c r="J85">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K85">
-        <v>657</v>
+        <v>721</v>
       </c>
       <c r="L85" s="2">
-        <v>46179.60576388889</v>
+        <v>46242.36850694445</v>
       </c>
       <c r="M85" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="N85" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O85" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="P85" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q85" t="s">
-        <v>259</v>
+        <v>265</v>
+      </c>
+      <c r="R85" t="s">
+        <v>263</v>
       </c>
       <c r="W85" s="2">
         <v>46168</v>
@@ -5931,25 +6234,25 @@
     </row>
     <row r="86" spans="1:23">
       <c r="A86" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C86" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D86" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E86" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F86" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G86" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H86">
         <v>5</v>
@@ -5961,25 +6264,28 @@
         <v>2</v>
       </c>
       <c r="K86">
-        <v>516</v>
+        <v>648</v>
       </c>
       <c r="L86" s="2">
-        <v>46179.60578703704</v>
+        <v>46242.36851851852</v>
       </c>
       <c r="M86" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="N86" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O86" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="P86" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q86" t="s">
-        <v>260</v>
+        <v>266</v>
+      </c>
+      <c r="R86" t="s">
+        <v>264</v>
       </c>
       <c r="W86" s="2">
         <v>46164</v>
@@ -5987,25 +6293,25 @@
     </row>
     <row r="87" spans="1:23">
       <c r="A87" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C87" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D87" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E87" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F87" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G87" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H87">
         <v>5</v>
@@ -6017,25 +6323,28 @@
         <v>30</v>
       </c>
       <c r="K87">
-        <v>1567</v>
+        <v>3547</v>
       </c>
       <c r="L87" s="2">
-        <v>46179.60581018519</v>
+        <v>46242.36854166666</v>
       </c>
       <c r="M87" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="N87" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O87" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="P87" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q87" t="s">
-        <v>260</v>
+        <v>266</v>
+      </c>
+      <c r="R87" t="s">
+        <v>264</v>
       </c>
       <c r="W87" s="2">
         <v>46168</v>
@@ -6043,25 +6352,25 @@
     </row>
     <row r="88" spans="1:23">
       <c r="A88" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C88" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D88" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E88" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F88" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G88" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H88">
         <v>5</v>
@@ -6073,25 +6382,28 @@
         <v>30</v>
       </c>
       <c r="K88">
-        <v>1511</v>
+        <v>3491</v>
       </c>
       <c r="L88" s="2">
-        <v>46179.6058449074</v>
+        <v>46242.36857638889</v>
       </c>
       <c r="M88" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="N88" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O88" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="P88" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q88" t="s">
-        <v>260</v>
+        <v>266</v>
+      </c>
+      <c r="R88" t="s">
+        <v>264</v>
       </c>
       <c r="W88" s="2">
         <v>46163</v>
@@ -6099,63 +6411,66 @@
     </row>
     <row r="89" spans="1:23">
       <c r="A89" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C89" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D89" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E89" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F89" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="G89" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H89">
         <v>5</v>
       </c>
       <c r="N89" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O89" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="P89" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q89" t="s">
-        <v>259</v>
+        <v>265</v>
+      </c>
+      <c r="R89" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="90" spans="1:23">
       <c r="A90" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C90" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D90" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E90" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F90" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G90" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H90">
         <v>5</v>
@@ -6167,25 +6482,28 @@
         <v>1</v>
       </c>
       <c r="K90">
-        <v>57</v>
+        <v>123</v>
       </c>
       <c r="L90" s="2">
-        <v>46179.60586805556</v>
+        <v>46242.36859953704</v>
       </c>
       <c r="M90" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="N90" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O90" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="P90" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q90" t="s">
-        <v>260</v>
+        <v>266</v>
+      </c>
+      <c r="R90" t="s">
+        <v>264</v>
       </c>
       <c r="W90" s="2">
         <v>46154</v>
@@ -6193,40 +6511,43 @@
     </row>
     <row r="91" spans="1:23">
       <c r="A91" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C91" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D91" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E91" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F91" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G91" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H91">
         <v>5</v>
       </c>
       <c r="N91" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O91" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="P91" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q91" t="s">
-        <v>260</v>
+        <v>266</v>
+      </c>
+      <c r="R91" t="s">
+        <v>264</v>
       </c>
       <c r="W91" s="2">
         <v>46154</v>
@@ -6234,25 +6555,25 @@
     </row>
     <row r="92" spans="1:23">
       <c r="A92" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C92" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D92" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E92" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F92" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="G92" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H92">
         <v>5</v>
@@ -6261,28 +6582,31 @@
         <v>1</v>
       </c>
       <c r="J92">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K92">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="L92" s="2">
-        <v>46179.60587962963</v>
+        <v>46242.36859953704</v>
       </c>
       <c r="M92" t="s">
         <v>258</v>
       </c>
       <c r="N92" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O92" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="P92" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q92" t="s">
-        <v>259</v>
+        <v>265</v>
+      </c>
+      <c r="R92" t="s">
+        <v>263</v>
       </c>
       <c r="W92" s="2">
         <v>46164</v>
